--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -763,10 +763,10 @@
         <v>4.4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
         <v>2.92</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
         <v>1.96</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
         <v>2.06</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
         <v>1.54</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
         <v>4.4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G6" t="n">
         <v>1.98</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>5.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Poli Iasi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>ASA Targu Mures</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Concordia Chiajna</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>CS Tunari</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>CSM Slatina</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ceahlaul</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1160,162 +1160,162 @@
         <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Afumati</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CSM Scolar Resita</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1354,162 +1354,162 @@
         <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>ACS Dumbravita</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>CSC 1599 Selimbar</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>ACS Fotbal Club Bacau</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CSM Satu Mare</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1742,7 +1742,7 @@
         <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,378 +1907,2318 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>CS Gloria 2018 Bistrita-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>CS FC Dinamo Bucuresti</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.34</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Australian A-League Men</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>06:35:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>07:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Spartak Varna</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dobrudzha</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Romanian Liga II</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Chindia Targoviste</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bihor Oradea</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CSKA 1948 Sofia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Romanian Liga II</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FC Voluntari</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FC Hunedoara</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ES Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K15" t="n">
+        <v>950</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Slavia Sofia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Septemvri</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Kabylie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K17" t="n">
+        <v>950</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Antalyaspor</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Italian Serie C</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>15:30:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>ASD Alcione</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Lecco</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-04-08 04:38:00</t>
+      <c r="Q19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R6" t="n">
         <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
         <v>2.4</v>
@@ -2133,13 +2133,13 @@
         <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.25</v>
@@ -2148,10 +2148,10 @@
         <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
         <v>2.88</v>
@@ -2166,76 +2166,76 @@
         <v>1.71</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH9" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP9" t="n">
         <v>16</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>15.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
         <v>7.8</v>
@@ -2247,7 +2247,7 @@
         <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2256,29 +2256,29 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BG9" t="n">
         <v>14</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2312,167 +2312,167 @@
         <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H10" t="n">
         <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="J10" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="R11" t="n">
         <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.65</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="H12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
         <v>5.8</v>
       </c>
-      <c r="I12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3100,155 +3100,155 @@
         <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.34</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,201 +4024,395 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 06:48:21</t>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Antalyaspor</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-08 08:59:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Italian Serie C</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>15:30:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>ASD Alcione</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Lecco</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-04-08 06:48:21</t>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-08 08:59:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
         <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2145,7 +2145,7 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.75</v>
@@ -2157,10 +2157,10 @@
         <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
         <v>1.71</v>
@@ -2169,116 +2169,116 @@
         <v>1.45</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2309,55 +2309,55 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.24</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>1.59</v>
       </c>
       <c r="O10" t="n">
         <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
         <v>1.33</v>
@@ -2396,7 +2396,7 @@
         <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>95</v>
@@ -2426,19 +2426,19 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>3.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AX10" t="n">
         <v>18</v>
@@ -2447,7 +2447,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.84</v>
+        <v>140</v>
       </c>
       <c r="J12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP12" t="n">
         <v>3.7</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AQ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW12" t="n">
         <v>21</v>
       </c>
-      <c r="AC12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>16</v>
       </c>
-      <c r="AX12" t="n">
-        <v>12</v>
-      </c>
       <c r="AY12" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
-        <v>19</v>
+        <v>3.85</v>
       </c>
       <c r="BB12" t="n">
-        <v>23</v>
+        <v>3.95</v>
       </c>
       <c r="BC12" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>19</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -2909,152 +2909,152 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
         <v>1.93</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O14" t="n">
         <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R14" t="n">
         <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
         <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
         <v>2.06</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="H19" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 08:59:19</t>
+          <t>2026-04-08 11:09:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q4" t="n">
         <v>1.19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q6" t="n">
         <v>1.37</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         <v>2.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
         <v>4.4</v>
@@ -2145,22 +2145,22 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
         <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
         <v>1.71</v>
@@ -2169,116 +2169,116 @@
         <v>1.45</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,16 +2333,16 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.59</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
         <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -2351,13 +2351,13 @@
         <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
         <v>1.33</v>
@@ -2420,25 +2420,25 @@
         <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.9</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.85</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
         <v>18</v>
@@ -2447,7 +2447,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.65</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="I12" t="n">
-        <v>140</v>
+        <v>2.66</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.27</v>
@@ -2721,34 +2721,34 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="S12" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
         <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
         <v>27</v>
@@ -2808,16 +2808,16 @@
         <v>3.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AS12" t="n">
         <v>3.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU12" t="n">
         <v>8.199999999999999</v>
@@ -2829,7 +2829,7 @@
         <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
@@ -2847,7 +2847,7 @@
         <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE12" t="n">
         <v>4</v>
@@ -2856,11 +2856,11 @@
         <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G13" t="n">
         <v>1.79</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
         <v>8</v>
@@ -2906,37 +2906,37 @@
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
         <v>1.14</v>
@@ -2945,116 +2945,116 @@
         <v>2.26</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>13</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AR13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BD13" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.84</v>
+        <v>4.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.84</v>
+        <v>4.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O14" t="n">
         <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Q14" t="n">
         <v>1.39</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="H16" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
         <v>6.2</v>
@@ -3685,159 +3685,159 @@
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H18" t="n">
         <v>2.28</v>
       </c>
-      <c r="H18" t="n">
-        <v>3.55</v>
-      </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>2.46</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,378 +4041,4064 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kolos Kovalyovka</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.44</v>
+        <v>6.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>2.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 11:09:53</t>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Slovenian Premier League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NK Primorje</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Koper</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>KTP</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>JaPS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Klubi-04</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hungarian NB I</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Puskas Akademia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gyori</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hermannstadt</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rapid Vienna (Am)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WSC Hertha Wels</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Austria Klagenfurt</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>KSV 1919</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Hobro</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AaB</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>IFK Mariehamn</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>KaPa</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SJK 2</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K29" t="n">
+        <v>950</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Wisla Plock</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HB Koge</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Middelfart</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Kabylie</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Esbjerg</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Hvidovre</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Antalyaspor</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hungarian NB I</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Diosgyori</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>950</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Italian Serie C</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>15:30:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>ASD Alcione</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Lecco</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-04-08 11:09:53</t>
+      <c r="Q37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>St Polten</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Korona Kielce</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystock</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:21:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH88"/>
+  <dimension ref="A1:BH90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2.38</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
@@ -2133,13 +2133,13 @@
         <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.26</v>
@@ -2163,7 +2163,7 @@
         <v>2.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -2208,13 +2208,13 @@
         <v>60</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
         <v>48</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
         <v>32</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT10" t="n">
         <v>9.199999999999999</v>
@@ -2438,41 +2438,41 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.95</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BA10" t="n">
         <v>4.2</v>
       </c>
       <c r="BB10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
         <v>4.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
         <v>21</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.26</v>
@@ -2721,76 +2721,76 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V12" t="n">
         <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB12" t="n">
         <v>17</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF12" t="n">
         <v>24</v>
       </c>
-      <c r="AA12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>25</v>
-      </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
         <v>40</v>
@@ -2799,68 +2799,68 @@
         <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="AS12" t="n">
         <v>30</v>
       </c>
       <c r="AT12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AX12" t="n">
         <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.4</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.3</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>1.28</v>
@@ -2954,7 +2954,7 @@
         <v>65</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB13" t="n">
         <v>8.6</v>
@@ -2999,16 +2999,16 @@
         <v>190</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.199999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="AQ13" t="n">
         <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT13" t="n">
         <v>5.4</v>
@@ -3017,13 +3017,13 @@
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.85</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
         <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AY13" t="n">
         <v>7.6</v>
@@ -3041,10 +3041,10 @@
         <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF13" t="n">
         <v>9.4</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
         <v>1.45</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="n">
         <v>2.58</v>
       </c>
       <c r="H16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
         <v>3.5</v>
@@ -3521,22 +3521,22 @@
         <v>1.85</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
         <v>1.63</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
         <v>11</v>
@@ -3545,16 +3545,16 @@
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>48</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>22</v>
@@ -3563,49 +3563,49 @@
         <v>70</v>
       </c>
       <c r="AJ16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK16" t="n">
         <v>36</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
         <v>160</v>
       </c>
       <c r="AN16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
         <v>6.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
@@ -3614,29 +3614,29 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.71</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H17" t="n">
         <v>5</v>
@@ -3718,7 +3718,7 @@
         <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
         <v>15</v>
@@ -3760,7 +3760,7 @@
         <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
         <v>46</v>
@@ -3784,7 +3784,7 @@
         <v>32</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -3796,7 +3796,7 @@
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
         <v>8.6</v>
@@ -3808,7 +3808,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
         <v>16</v>
@@ -3820,17 +3820,17 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
         <v>11.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
         <v>3.3</v>
@@ -3873,10 +3873,10 @@
         <v>2.42</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3894,16 +3894,16 @@
         <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
         <v>2.28</v>
@@ -3924,7 +3924,7 @@
         <v>970</v>
       </c>
       <c r="AA18" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AB18" t="n">
         <v>970</v>
@@ -3933,7 +3933,7 @@
         <v>970</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3951,80 +3951,80 @@
         <v>36</v>
       </c>
       <c r="AJ18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
         <v>36</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO18" t="n">
         <v>970</v>
       </c>
       <c r="AP18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX18" t="n">
         <v>3.2</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW18" t="n">
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD18" t="n">
         <v>3.35</v>
       </c>
-      <c r="AX18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.94</v>
-      </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
         <v>12.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4055,40 +4055,40 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
@@ -4097,49 +4097,49 @@
         <v>1.01</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X19" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AA19" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AG19" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI19" t="n">
         <v>85</v>
@@ -4160,65 +4160,65 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="BG19" t="n">
-        <v>18</v>
+        <v>2.52</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4357,10 +4357,10 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR20" t="n">
         <v>4.2</v>
@@ -4372,7 +4372,7 @@
         <v>11.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
@@ -4381,16 +4381,16 @@
         <v>4.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB20" t="n">
         <v>10.5</v>
@@ -4408,11 +4408,11 @@
         <v>3.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="I21" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -4464,13 +4464,13 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.88</v>
+        <v>6.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="P21" t="n">
         <v>2.88</v>
@@ -4479,134 +4479,134 @@
         <v>1.43</v>
       </c>
       <c r="R21" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
         <v>4.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
         <v>950</v>
@@ -5843,7 +5843,7 @@
         <v>1.87</v>
       </c>
       <c r="T28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
         <v>19.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB29" t="n">
         <v>13.5</v>
@@ -6139,13 +6139,13 @@
         <v>6.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="BC29" t="n">
         <v>6.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BE29" t="n">
         <v>7.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="H30" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I30" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6237,10 +6237,10 @@
         <v>1.66</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W30" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>85</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR30" t="n">
         <v>17</v>
       </c>
       <c r="AS30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>2.3</v>
       </c>
-      <c r="AT30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW30" t="n">
+      <c r="BA30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC30" t="n">
         <v>2.28</v>
       </c>
-      <c r="AX30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.24</v>
-      </c>
       <c r="BD30" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BF30" t="n">
         <v>14</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -6885,10 +6885,10 @@
         <v>13.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT33" t="n">
         <v>7.2</v>
@@ -6912,7 +6912,7 @@
         <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB33" t="n">
         <v>14.5</v>
@@ -6921,10 +6921,10 @@
         <v>13.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF33" t="n">
         <v>7.8</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
         <v>32</v>
       </c>
       <c r="AJ34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK34" t="n">
         <v>34</v>
@@ -7064,7 +7064,7 @@
         <v>38</v>
       </c>
       <c r="AM34" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN34" t="n">
         <v>23</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
         <v>12</v>
       </c>
       <c r="AG35" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH35" t="n">
         <v>48</v>
@@ -7273,10 +7273,10 @@
         <v>10.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
         <v>4.1</v>
@@ -7288,7 +7288,7 @@
         <v>1.03</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
         <v>7</v>
@@ -7297,32 +7297,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
         <v>18</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
         <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="R36" t="n">
         <v>1.34</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -7747,10 +7747,10 @@
         <v>2.28</v>
       </c>
       <c r="H38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I38" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>3.6</v>
@@ -7771,7 +7771,7 @@
         <v>1.23</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q38" t="n">
         <v>1.78</v>
@@ -7789,7 +7789,7 @@
         <v>2.1</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
         <v>1.78</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
         <v>1.03</v>
       </c>
       <c r="N40" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O40" t="n">
         <v>1.17</v>
@@ -8165,16 +8165,16 @@
         <v>1.53</v>
       </c>
       <c r="R40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S40" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T40" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U40" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V40" t="n">
         <v>1.08</v>
@@ -8183,10 +8183,10 @@
         <v>3.9</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y40" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z40" t="n">
         <v>1000</v>
@@ -8195,104 +8195,104 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AC40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>20</v>
       </c>
-      <c r="AD40" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA40" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="BB40" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>2.58</v>
+        <v>25</v>
       </c>
       <c r="BE40" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="BF40" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v>3.05</v>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>3.05</v>
@@ -8347,7 +8347,7 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.4</v>
@@ -8356,7 +8356,7 @@
         <v>1.69</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R41" t="n">
         <v>1.2</v>
@@ -8374,7 +8374,7 @@
         <v>1.33</v>
       </c>
       <c r="W41" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -8559,13 +8559,13 @@
         <v>2.38</v>
       </c>
       <c r="T42" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W42" t="n">
         <v>1.92</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -8896,32 +8896,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury Merogis</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="G44" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="H44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K44" t="n">
         <v>4.1</v>
       </c>
-      <c r="I44" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
@@ -8929,22 +8929,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="O44" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R44" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S44" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -8953,10 +8953,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W44" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -9090,31 +9090,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fleury Merogis</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="G45" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="H45" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="I45" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="J45" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -9123,22 +9123,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="O45" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P45" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R45" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S45" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -9147,10 +9147,10 @@
         <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W45" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -9511,16 +9511,16 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="O47" t="n">
         <v>1.27</v>
       </c>
       <c r="P47" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="R47" t="n">
         <v>1.28</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -9899,16 +9899,16 @@
         <v>1.03</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O49" t="n">
         <v>1.18</v>
       </c>
       <c r="P49" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="R49" t="n">
         <v>1.5</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
         <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N51" t="n">
         <v>1.02</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -10657,70 +10657,70 @@
         <v>2.36</v>
       </c>
       <c r="H53" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="K53" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
       </c>
       <c r="M53" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N53" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O53" t="n">
         <v>1.36</v>
       </c>
       <c r="P53" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R53" t="n">
         <v>1.24</v>
       </c>
       <c r="S53" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T53" t="n">
         <v>1.73</v>
       </c>
       <c r="U53" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V53" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W53" t="n">
         <v>1.73</v>
       </c>
       <c r="X53" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z53" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA53" t="n">
         <v>80</v>
       </c>
       <c r="AB53" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC53" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD53" t="n">
         <v>970</v>
@@ -10729,92 +10729,92 @@
         <v>55</v>
       </c>
       <c r="AF53" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG53" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI53" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ53" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AK53" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AL53" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO53" t="n">
         <v>60</v>
       </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>55</v>
-      </c>
       <c r="AP53" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR53" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AS53" t="n">
-        <v>48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.76</v>
+        <v>6.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW53" t="n">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="AX53" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY53" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="AZ53" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BA53" t="n">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="BB53" t="n">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC53" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="BD53" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE53" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF53" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BG53" t="n">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G54" t="n">
         <v>5.2</v>
@@ -10869,7 +10869,7 @@
         <v>1.08</v>
       </c>
       <c r="N54" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
         <v>1.37</v>
@@ -10881,10 +10881,10 @@
         <v>2.12</v>
       </c>
       <c r="R54" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T54" t="n">
         <v>1.94</v>
@@ -10932,7 +10932,7 @@
         <v>23</v>
       </c>
       <c r="AI54" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ54" t="n">
         <v>140</v>
@@ -10941,7 +10941,7 @@
         <v>75</v>
       </c>
       <c r="AL54" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="n">
         <v>160</v>
@@ -10986,7 +10986,7 @@
         <v>6.6</v>
       </c>
       <c r="BA54" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB54" t="n">
         <v>8.800000000000001</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -11039,13 +11039,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G55" t="n">
         <v>2.88</v>
       </c>
       <c r="H55" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I55" t="n">
         <v>2.72</v>
@@ -11117,10 +11117,10 @@
         <v>27</v>
       </c>
       <c r="AF55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG55" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH55" t="n">
         <v>17</v>
@@ -11129,19 +11129,19 @@
         <v>36</v>
       </c>
       <c r="AJ55" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK55" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL55" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM55" t="n">
         <v>75</v>
       </c>
       <c r="AN55" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO55" t="n">
         <v>17.5</v>
@@ -11156,7 +11156,7 @@
         <v>15.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT55" t="n">
         <v>11.5</v>
@@ -11180,19 +11180,19 @@
         <v>13.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB55" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC55" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD55" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF55" t="n">
         <v>16.5</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -11463,10 +11463,10 @@
         <v>1.35</v>
       </c>
       <c r="R57" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S57" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="T57" t="n">
         <v>1.93</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -11660,10 +11660,10 @@
         <v>1.57</v>
       </c>
       <c r="S58" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="T58" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U58" t="n">
         <v>2.56</v>
@@ -11729,13 +11729,13 @@
         <v>17</v>
       </c>
       <c r="AP58" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ58" t="n">
         <v>11.5</v>
       </c>
       <c r="AR58" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AS58" t="n">
         <v>4.5</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -12400,10 +12400,10 @@
         <v>2.82</v>
       </c>
       <c r="G62" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="H62" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="I62" t="n">
         <v>2.74</v>
@@ -12448,7 +12448,7 @@
         <v>1.58</v>
       </c>
       <c r="W62" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -12594,10 +12594,10 @@
         <v>2.94</v>
       </c>
       <c r="G63" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="H63" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="I63" t="n">
         <v>2.68</v>
@@ -12642,7 +12642,7 @@
         <v>1.59</v>
       </c>
       <c r="W63" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -12839,10 +12839,10 @@
         <v>1.85</v>
       </c>
       <c r="X64" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y64" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z64" t="n">
         <v>29</v>
@@ -12857,19 +12857,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD64" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE64" t="n">
         <v>44</v>
       </c>
       <c r="AF64" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG64" t="n">
         <v>11</v>
       </c>
       <c r="AH64" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI64" t="n">
         <v>48</v>
@@ -12884,25 +12884,25 @@
         <v>34</v>
       </c>
       <c r="AM64" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN64" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AO64" t="n">
         <v>40</v>
       </c>
       <c r="AP64" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ64" t="n">
         <v>7</v>
       </c>
       <c r="AR64" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS64" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AT64" t="n">
         <v>9.4</v>
@@ -12914,7 +12914,7 @@
         <v>7</v>
       </c>
       <c r="AW64" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX64" t="n">
         <v>12</v>
@@ -12935,7 +12935,7 @@
         <v>7.6</v>
       </c>
       <c r="BD64" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE64" t="n">
         <v>10.5</v>
@@ -12944,11 +12944,11 @@
         <v>6.4</v>
       </c>
       <c r="BG64" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
         <v>1.05</v>
       </c>
       <c r="N68" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O68" t="n">
         <v>1.22</v>
@@ -13597,13 +13597,13 @@
         <v>1.68</v>
       </c>
       <c r="R68" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S68" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T68" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U68" t="n">
         <v>2.38</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -13764,10 +13764,10 @@
         <v>2.16</v>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J69" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K69" t="n">
         <v>4</v>
@@ -13803,7 +13803,7 @@
         <v>2.64</v>
       </c>
       <c r="V69" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W69" t="n">
         <v>1.39</v>
@@ -13830,7 +13830,7 @@
         <v>11</v>
       </c>
       <c r="AE69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF69" t="n">
         <v>28</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -14340,10 +14340,10 @@
         <v>1.37</v>
       </c>
       <c r="G72" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H72" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I72" t="n">
         <v>12</v>
@@ -14442,7 +14442,7 @@
         <v>6.8</v>
       </c>
       <c r="AO72" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="AP72" t="n">
         <v>14</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -14621,10 +14621,10 @@
         <v>40</v>
       </c>
       <c r="AJ73" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK73" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL73" t="n">
         <v>55</v>
@@ -14687,14 +14687,14 @@
         <v>10.5</v>
       </c>
       <c r="BF73" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG73" t="n">
         <v>16</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14767,7 @@
         <v>3.35</v>
       </c>
       <c r="T74" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U74" t="n">
         <v>1.8</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -14922,7 +14922,7 @@
         <v>1.35</v>
       </c>
       <c r="G75" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H75" t="n">
         <v>9.800000000000001</v>
@@ -14952,7 +14952,7 @@
         <v>2.06</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R75" t="n">
         <v>1.34</v>
@@ -14970,7 +14970,7 @@
         <v>1.07</v>
       </c>
       <c r="W75" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -15698,19 +15698,19 @@
         <v>2.5</v>
       </c>
       <c r="G79" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="H79" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="I79" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J79" t="n">
         <v>2.88</v>
       </c>
       <c r="K79" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -15743,11 +15743,11 @@
         <v>1.01</v>
       </c>
       <c r="V79" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W79" t="n">
         <v>1.41</v>
       </c>
-      <c r="W79" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X79" t="n">
         <v>1000</v>
       </c>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
         <v>3.85</v>
       </c>
       <c r="H80" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I80" t="n">
         <v>2.88</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16125,7 @@
         <v>3.25</v>
       </c>
       <c r="T81" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U81" t="n">
         <v>2.16</v>
@@ -16218,7 +16218,7 @@
         <v>11</v>
       </c>
       <c r="AY81" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ81" t="n">
         <v>17</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16504,7 @@
         <v>3.15</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R83" t="n">
         <v>1.88</v>
@@ -16528,13 +16528,13 @@
         <v>36</v>
       </c>
       <c r="Y83" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z83" t="n">
         <v>110</v>
       </c>
       <c r="AA83" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AB83" t="n">
         <v>13.5</v>
@@ -16543,7 +16543,7 @@
         <v>15</v>
       </c>
       <c r="AD83" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE83" t="n">
         <v>130</v>
@@ -16582,7 +16582,7 @@
         <v>32</v>
       </c>
       <c r="AQ83" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR83" t="n">
         <v>38</v>
@@ -16594,7 +16594,7 @@
         <v>12</v>
       </c>
       <c r="AU83" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV83" t="n">
         <v>32</v>
@@ -16615,16 +16615,16 @@
         <v>36</v>
       </c>
       <c r="BB83" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC83" t="n">
         <v>12</v>
       </c>
       <c r="BD83" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE83" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="BF83" t="n">
         <v>3.65</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
         <v>1.28</v>
       </c>
       <c r="G84" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="H84" t="n">
         <v>12.5</v>
@@ -16677,7 +16677,7 @@
         <v>14</v>
       </c>
       <c r="J84" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K84" t="n">
         <v>7.2</v>
@@ -16713,10 +16713,10 @@
         <v>1.92</v>
       </c>
       <c r="V84" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W84" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X84" t="n">
         <v>40</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G85" t="n">
         <v>1.63</v>
@@ -16880,10 +16880,10 @@
         <v>1.01</v>
       </c>
       <c r="M85" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N85" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="O85" t="n">
         <v>1.37</v>
@@ -16895,16 +16895,16 @@
         <v>2.06</v>
       </c>
       <c r="R85" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S85" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T85" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U85" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V85" t="n">
         <v>1.14</v>
@@ -16913,116 +16913,116 @@
         <v>2.58</v>
       </c>
       <c r="X85" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y85" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z85" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA85" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AB85" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV85" t="n">
         <v>8</v>
       </c>
-      <c r="AC85" t="n">
+      <c r="AW85" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE85" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD85" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG85" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH85" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI85" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AS85" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT85" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU85" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV85" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW85" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX85" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB85" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC85" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BF85" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG85" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
@@ -17247,13 +17247,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G87" t="n">
         <v>3.7</v>
       </c>
       <c r="H87" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I87" t="n">
         <v>2.86</v>
@@ -17262,7 +17262,7 @@
         <v>3.05</v>
       </c>
       <c r="K87" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -17410,201 +17410,589 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S88" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:19:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I89" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K89" t="n">
+        <v>950</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W89" t="n">
+        <v>2</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH89" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:19:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Sportivo San Lorenzo</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Guarani (Par)</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="F90" t="n">
         <v>3.45</v>
       </c>
-      <c r="G88" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I88" t="n">
+      <c r="G90" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I90" t="n">
         <v>2.34</v>
       </c>
-      <c r="J88" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K88" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
+      <c r="J90" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P90" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="Q90" t="n">
         <v>2.08</v>
       </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" t="n">
-        <v>0</v>
-      </c>
-      <c r="X88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH88" t="inlineStr">
-        <is>
-          <t>2026-04-08 20:04:15</t>
+      <c r="R90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
@@ -1196,7 +1196,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2175,52 +2175,52 @@
         <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA9" t="n">
         <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
         <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
         <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AP9" t="n">
         <v>16</v>
@@ -2232,7 +2232,7 @@
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2256,29 +2256,29 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
         <v>38</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
         <v>14</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I10" t="n">
         <v>2.56</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
         <v>2.86</v>
       </c>
       <c r="H12" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
@@ -2730,13 +2730,13 @@
         <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
         <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
         <v>1.61</v>
@@ -2745,22 +2745,22 @@
         <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
         <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="n">
         <v>16.5</v>
@@ -2769,16 +2769,16 @@
         <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
         <v>27</v>
       </c>
       <c r="AF12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
@@ -2787,7 +2787,7 @@
         <v>38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
         <v>32</v>
@@ -2802,13 +2802,13 @@
         <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
         <v>16.5</v>
@@ -2817,7 +2817,7 @@
         <v>30</v>
       </c>
       <c r="AT12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
@@ -2826,7 +2826,7 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>18</v>
@@ -2841,10 +2841,10 @@
         <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BD12" t="n">
         <v>29</v>
@@ -2853,14 +2853,14 @@
         <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H16" t="n">
         <v>3.05</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
         <v>3.1</v>
@@ -3515,16 +3515,16 @@
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
         <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
@@ -3533,10 +3533,10 @@
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
         <v>11</v>
@@ -3548,7 +3548,7 @@
         <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
         <v>15.5</v>
@@ -3566,13 +3566,13 @@
         <v>40</v>
       </c>
       <c r="AK16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN16" t="n">
         <v>36</v>
@@ -3587,40 +3587,40 @@
         <v>5.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
         <v>5.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
         <v>3.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD16" t="n">
         <v>9.4</v>
@@ -3629,14 +3629,14 @@
         <v>3.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="BG16" t="n">
         <v>3.25</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.72</v>
       </c>
       <c r="G17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H17" t="n">
         <v>5</v>
@@ -3718,7 +3718,7 @@
         <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X17" t="n">
         <v>15</v>
@@ -3727,7 +3727,7 @@
         <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA17" t="n">
         <v>170</v>
@@ -3742,7 +3742,7 @@
         <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF17" t="n">
         <v>11</v>
@@ -3757,13 +3757,13 @@
         <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK17" t="n">
         <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
         <v>170</v>
@@ -3775,13 +3775,13 @@
         <v>130</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
         <v>7.8</v>
@@ -3793,44 +3793,44 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
         <v>7.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
         <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG17" t="n">
         <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
         <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="I18" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
@@ -3894,7 +3894,7 @@
         <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
@@ -3912,7 +3912,7 @@
         <v>1.71</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
         <v>20</v>
@@ -3930,7 +3930,7 @@
         <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -3948,7 +3948,7 @@
         <v>970</v>
       </c>
       <c r="AI18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
         <v>55</v>
@@ -3969,62 +3969,62 @@
         <v>970</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18" t="n">
         <v>12.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>2.48</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L19" t="n">
         <v>1.54</v>
@@ -4133,13 +4133,13 @@
         <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AG19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4172,7 +4172,7 @@
         <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AT19" t="n">
         <v>3.7</v>
@@ -4184,41 +4184,41 @@
         <v>4</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
         <v>1.52</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>5.3</v>
@@ -4270,10 +4270,10 @@
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.12</v>
@@ -4282,25 +4282,25 @@
         <v>3.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="R20" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
         <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4321,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
@@ -4333,7 +4333,7 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4351,7 +4351,7 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -4369,50 +4369,50 @@
         <v>4.3</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
         <v>4.2</v>
       </c>
       <c r="AX20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY20" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY20" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
         <v>4.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>17.5</v>
       </c>
       <c r="BE20" t="n">
         <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG20" t="n">
         <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G21" t="n">
         <v>2.44</v>
@@ -4452,13 +4452,13 @@
         <v>2.8</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,130 +4467,130 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P21" t="n">
         <v>2.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.69</v>
       </c>
       <c r="X21" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA21" t="n">
         <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
         <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM21" t="n">
         <v>55</v>
       </c>
       <c r="AN21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY21" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
       </c>
       <c r="AZ21" t="n">
         <v>12</v>
       </c>
       <c r="BA21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB21" t="n">
         <v>22</v>
       </c>
-      <c r="BB21" t="n">
-        <v>24</v>
-      </c>
       <c r="BC21" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
         <v>20</v>
@@ -4599,14 +4599,14 @@
         <v>32</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H23" t="n">
         <v>1.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4864,7 +4864,7 @@
         <v>1.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="R23" t="n">
         <v>1.34</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>3.15</v>
       </c>
       <c r="H24" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I24" t="n">
         <v>2.78</v>
@@ -5040,19 +5040,19 @@
         <v>3.4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
         <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
         <v>1.97</v>
@@ -5061,16 +5061,16 @@
         <v>1.83</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
         <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
         <v>1.56</v>
@@ -5079,28 +5079,28 @@
         <v>1.47</v>
       </c>
       <c r="X24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB24" t="n">
         <v>14.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
         <v>25</v>
@@ -5112,10 +5112,10 @@
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK24" t="n">
         <v>38</v>
@@ -5130,65 +5130,65 @@
         <v>34</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
         <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="BG24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G25" t="n">
         <v>3.25</v>
@@ -5228,7 +5228,7 @@
         <v>2.54</v>
       </c>
       <c r="I25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
         <v>3.3</v>
@@ -5249,7 +5249,7 @@
         <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
         <v>1.84</v>
@@ -5267,7 +5267,7 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W25" t="n">
         <v>1.44</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>2.72</v>
       </c>
       <c r="G26" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="H26" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="I26" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,19 +5437,19 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
         <v>3.05</v>
@@ -5461,10 +5461,10 @@
         <v>2.22</v>
       </c>
       <c r="V26" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W26" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
         <v>19.5</v>
@@ -5473,70 +5473,70 @@
         <v>14.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB26" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF26" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP26" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
         <v>8.800000000000001</v>
@@ -5545,38 +5545,38 @@
         <v>20</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N28" t="n">
         <v>1.01</v>
@@ -5843,7 +5843,7 @@
         <v>1.87</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="U28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>2.68</v>
       </c>
       <c r="G29" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I29" t="n">
         <v>2.84</v>
@@ -6010,7 +6010,7 @@
         <v>3.35</v>
       </c>
       <c r="K29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6028,13 +6028,13 @@
         <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R29" t="n">
         <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
         <v>1.68</v>
@@ -6046,10 +6046,10 @@
         <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y29" t="n">
         <v>13</v>
@@ -6112,7 +6112,7 @@
         <v>15.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT29" t="n">
         <v>10.5</v>
@@ -6145,10 +6145,10 @@
         <v>6.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF29" t="n">
         <v>21</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6198,10 +6198,10 @@
         <v>3.3</v>
       </c>
       <c r="I30" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="K30" t="n">
         <v>4.2</v>
@@ -6219,7 +6219,7 @@
         <v>1.38</v>
       </c>
       <c r="P30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q30" t="n">
         <v>2.16</v>
@@ -6231,13 +6231,13 @@
         <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="V30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W30" t="n">
         <v>1.6</v>
@@ -6279,7 +6279,7 @@
         <v>90</v>
       </c>
       <c r="AJ30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK30" t="n">
         <v>40</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G31" t="n">
         <v>2.2</v>
@@ -6392,10 +6392,10 @@
         <v>3.45</v>
       </c>
       <c r="I31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J31" t="n">
         <v>3.8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.75</v>
       </c>
       <c r="K31" t="n">
         <v>4</v>
@@ -6431,7 +6431,7 @@
         <v>2.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
         <v>1.83</v>
@@ -6446,13 +6446,13 @@
         <v>34</v>
       </c>
       <c r="AA31" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB31" t="n">
         <v>15</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD31" t="n">
         <v>18.5</v>
@@ -6464,7 +6464,7 @@
         <v>18.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
         <v>19.5</v>
@@ -6485,7 +6485,7 @@
         <v>85</v>
       </c>
       <c r="AN31" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO31" t="n">
         <v>36</v>
@@ -6497,10 +6497,10 @@
         <v>15</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AT31" t="n">
         <v>10.5</v>
@@ -6512,7 +6512,7 @@
         <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AX31" t="n">
         <v>11</v>
@@ -6524,7 +6524,7 @@
         <v>11.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -6533,20 +6533,20 @@
         <v>17.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF31" t="n">
         <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="G32" t="n">
         <v>18</v>
@@ -6589,7 +6589,7 @@
         <v>1.32</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>1.09</v>
       </c>
       <c r="K32" t="n">
         <v>7.6</v>
@@ -6598,7 +6598,7 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N32" t="n">
         <v>2.68</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6771,61 +6771,61 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G33" t="n">
         <v>1.86</v>
       </c>
       <c r="H33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I33" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J33" t="n">
         <v>3.75</v>
       </c>
       <c r="K33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.26</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R33" t="n">
         <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T33" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U33" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V33" t="n">
         <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X33" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Y33" t="n">
         <v>19.5</v>
@@ -6840,13 +6840,13 @@
         <v>10.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD33" t="n">
         <v>20</v>
       </c>
       <c r="AE33" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF33" t="n">
         <v>12.5</v>
@@ -6870,49 +6870,49 @@
         <v>34</v>
       </c>
       <c r="AM33" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
         <v>11.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP33" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>13.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ33" t="n">
         <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BB33" t="n">
         <v>14.5</v>
@@ -6921,20 +6921,20 @@
         <v>13.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G34" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="H34" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="I34" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="J34" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -7007,67 +7007,67 @@
         <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U34" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="V34" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="W34" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y34" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA34" t="n">
         <v>32</v>
       </c>
       <c r="AB34" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF34" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH34" t="n">
         <v>16</v>
       </c>
       <c r="AI34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ34" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL34" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM34" t="n">
         <v>65</v>
       </c>
       <c r="AN34" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO34" t="n">
         <v>13.5</v>
@@ -7076,31 +7076,31 @@
         <v>18.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR34" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU34" t="n">
         <v>8</v>
       </c>
       <c r="AV34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ34" t="n">
         <v>13</v>
@@ -7109,26 +7109,26 @@
         <v>21</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
         <v>2.26</v>
       </c>
       <c r="O35" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P35" t="n">
         <v>1.41</v>
@@ -7219,7 +7219,7 @@
         <v>14.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA35" t="n">
         <v>350</v>
@@ -7240,16 +7240,16 @@
         <v>10</v>
       </c>
       <c r="AG35" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AI35" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AJ35" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK35" t="n">
         <v>38</v>
@@ -7261,68 +7261,68 @@
         <v>530</v>
       </c>
       <c r="AN35" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO35" t="n">
         <v>540</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT35" t="n">
         <v>4.1</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>28</v>
+        <v>5.6</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7356,16 +7356,16 @@
         <v>2.68</v>
       </c>
       <c r="G36" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H36" t="n">
         <v>2.56</v>
       </c>
       <c r="I36" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K36" t="n">
         <v>3.85</v>
@@ -7401,10 +7401,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>1.71</v>
       </c>
       <c r="G37" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H37" t="n">
         <v>4.6</v>
@@ -7598,7 +7598,7 @@
         <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X37" t="n">
         <v>30</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7744,10 +7744,10 @@
         <v>2.1</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I38" t="n">
         <v>3.8</v>
@@ -7759,7 +7759,7 @@
         <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -7777,7 +7777,7 @@
         <v>1.78</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S38" t="n">
         <v>2.6</v>
@@ -7792,7 +7792,7 @@
         <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>3.9</v>
       </c>
       <c r="G39" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H39" t="n">
         <v>1.98</v>
@@ -7959,22 +7959,22 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O39" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P39" t="n">
         <v>2.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T39" t="n">
         <v>1.66</v>
@@ -7986,31 +7986,31 @@
         <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X39" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y39" t="n">
         <v>11.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB39" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC39" t="n">
         <v>9</v>
       </c>
       <c r="AD39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF39" t="n">
         <v>32</v>
@@ -8040,13 +8040,13 @@
         <v>38</v>
       </c>
       <c r="AO39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR39" t="n">
         <v>12</v>
@@ -8079,7 +8079,7 @@
         <v>26</v>
       </c>
       <c r="BB39" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BC39" t="n">
         <v>38</v>
@@ -8088,7 +8088,7 @@
         <v>40</v>
       </c>
       <c r="BE39" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BF39" t="n">
         <v>30</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8156,25 +8156,25 @@
         <v>5.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P40" t="n">
         <v>2.58</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R40" t="n">
         <v>1.64</v>
       </c>
       <c r="S40" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U40" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V40" t="n">
         <v>1.08</v>
@@ -8186,7 +8186,7 @@
         <v>30</v>
       </c>
       <c r="Y40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z40" t="n">
         <v>130</v>
@@ -8246,7 +8246,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT40" t="n">
         <v>9</v>
@@ -8258,7 +8258,7 @@
         <v>34</v>
       </c>
       <c r="AW40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX40" t="n">
         <v>7.6</v>
@@ -8270,7 +8270,7 @@
         <v>20</v>
       </c>
       <c r="BA40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB40" t="n">
         <v>9.199999999999999</v>
@@ -8288,11 +8288,11 @@
         <v>3.85</v>
       </c>
       <c r="BG40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G41" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H41" t="n">
         <v>3.9</v>
@@ -8353,7 +8353,7 @@
         <v>1.36</v>
       </c>
       <c r="P41" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q41" t="n">
         <v>2.06</v>
@@ -8374,7 +8374,7 @@
         <v>1.22</v>
       </c>
       <c r="W41" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -8714,16 +8714,16 @@
         <v>2.28</v>
       </c>
       <c r="G43" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H43" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I43" t="n">
         <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K43" t="n">
         <v>3.6</v>
@@ -8762,7 +8762,7 @@
         <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9102,10 +9102,10 @@
         <v>1.85</v>
       </c>
       <c r="G45" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H45" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I45" t="n">
         <v>5</v>
@@ -9150,7 +9150,7 @@
         <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9317,7 +9317,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O46" t="n">
         <v>1.27</v>
@@ -9326,7 +9326,7 @@
         <v>1.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R46" t="n">
         <v>1.28</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -9681,10 +9681,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="G48" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H48" t="n">
         <v>4</v>
@@ -9720,7 +9720,7 @@
         <v>1.5</v>
       </c>
       <c r="S48" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T48" t="n">
         <v>1.5</v>
@@ -9732,7 +9732,7 @@
         <v>1.27</v>
       </c>
       <c r="W48" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9741,7 +9741,7 @@
         <v>30</v>
       </c>
       <c r="Z48" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA48" t="n">
         <v>1000</v>
@@ -9753,10 +9753,10 @@
         <v>14.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF48" t="n">
         <v>19</v>
@@ -9768,7 +9768,7 @@
         <v>23</v>
       </c>
       <c r="AI48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ48" t="n">
         <v>29</v>
@@ -9780,71 +9780,71 @@
         <v>38</v>
       </c>
       <c r="AM48" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN48" t="n">
         <v>11.5</v>
       </c>
       <c r="AO48" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AR48" t="n">
         <v>23</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AT48" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AX48" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY48" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BA48" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG48" t="n">
         <v>2.62</v>
       </c>
-      <c r="BB48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
         <v>1.33</v>
       </c>
       <c r="P50" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q50" t="n">
         <v>1.86</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10263,43 +10263,43 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="G51" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="H51" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I51" t="n">
         <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K51" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N51" t="n">
-        <v>1.02</v>
+        <v>2.54</v>
       </c>
       <c r="O51" t="n">
         <v>1.12</v>
       </c>
       <c r="P51" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="Q51" t="n">
         <v>1.36</v>
       </c>
       <c r="R51" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S51" t="n">
         <v>1.98</v>
@@ -10314,7 +10314,7 @@
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10487,7 +10487,7 @@
         <v>1.4</v>
       </c>
       <c r="P52" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q52" t="n">
         <v>2.16</v>
@@ -10496,10 +10496,10 @@
         <v>1.28</v>
       </c>
       <c r="S52" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T52" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U52" t="n">
         <v>2</v>
@@ -10541,10 +10541,10 @@
         <v>970</v>
       </c>
       <c r="AH52" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI52" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ52" t="n">
         <v>32</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10657,164 +10657,164 @@
         <v>5.3</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="I53" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J53" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K53" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L53" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M53" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N53" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
         <v>1.33</v>
       </c>
       <c r="P53" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Q53" t="n">
         <v>1.98</v>
       </c>
       <c r="R53" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T53" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U53" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="V53" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W53" t="n">
         <v>1.23</v>
       </c>
       <c r="X53" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y53" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD53" t="n">
         <v>11</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE53" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AF53" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AG53" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AH53" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AI53" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL53" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN53" t="n">
         <v>85</v>
       </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>110</v>
-      </c>
       <c r="AO53" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AP53" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ53" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR53" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS53" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV53" t="n">
         <v>9</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.75</v>
+        <v>16.5</v>
       </c>
       <c r="AX53" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.72</v>
+        <v>15.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA53" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.86</v>
+        <v>8</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.82</v>
+        <v>7.6</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.82</v>
+        <v>7.6</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.86</v>
+        <v>8</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.83</v>
+        <v>7.6</v>
       </c>
       <c r="BG53" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -10845,22 +10845,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G54" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H54" t="n">
         <v>2.5</v>
       </c>
       <c r="I54" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J54" t="n">
         <v>3.75</v>
       </c>
       <c r="K54" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -10878,7 +10878,7 @@
         <v>2.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R54" t="n">
         <v>1.48</v>
@@ -10896,7 +10896,7 @@
         <v>1.58</v>
       </c>
       <c r="W54" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X54" t="n">
         <v>23</v>
@@ -10962,7 +10962,7 @@
         <v>15.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>29</v>
+        <v>7.6</v>
       </c>
       <c r="AT54" t="n">
         <v>11.5</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11039,16 +11039,16 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G55" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="H55" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I55" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J55" t="n">
         <v>3.15</v>
@@ -11081,28 +11081,28 @@
         <v>3.4</v>
       </c>
       <c r="T55" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U55" t="n">
         <v>1.69</v>
       </c>
       <c r="V55" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W55" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z55" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA55" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB55" t="n">
         <v>14.5</v>
@@ -11111,16 +11111,16 @@
         <v>10.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE55" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG55" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH55" t="n">
         <v>28</v>
@@ -11144,65 +11144,65 @@
         <v>48</v>
       </c>
       <c r="AO55" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR55" t="n">
         <v>12</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="AX55" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AY55" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BB55" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="BE55" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BF55" t="n">
         <v>19</v>
       </c>
       <c r="BG55" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11269,13 +11269,13 @@
         <v>1.8</v>
       </c>
       <c r="R56" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U56" t="n">
         <v>2.06</v>
@@ -11299,7 +11299,7 @@
         <v>150</v>
       </c>
       <c r="AB56" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC56" t="n">
         <v>9.6</v>
@@ -11311,7 +11311,7 @@
         <v>70</v>
       </c>
       <c r="AF56" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG56" t="n">
         <v>10.5</v>
@@ -11338,7 +11338,7 @@
         <v>10.5</v>
       </c>
       <c r="AO56" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP56" t="n">
         <v>14.5</v>
@@ -11347,10 +11347,10 @@
         <v>16</v>
       </c>
       <c r="AR56" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AS56" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT56" t="n">
         <v>8.199999999999999</v>
@@ -11362,7 +11362,7 @@
         <v>17</v>
       </c>
       <c r="AW56" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX56" t="n">
         <v>9.800000000000001</v>
@@ -11374,7 +11374,7 @@
         <v>16.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB56" t="n">
         <v>16</v>
@@ -11383,20 +11383,20 @@
         <v>15.5</v>
       </c>
       <c r="BD56" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE56" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF56" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG56" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
         <v>1.26</v>
       </c>
       <c r="M57" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N57" t="n">
         <v>5.1</v>
@@ -11466,10 +11466,10 @@
         <v>1.57</v>
       </c>
       <c r="S57" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="T57" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U57" t="n">
         <v>2.56</v>
@@ -11490,7 +11490,7 @@
         <v>24</v>
       </c>
       <c r="AA57" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB57" t="n">
         <v>19</v>
@@ -11517,7 +11517,7 @@
         <v>36</v>
       </c>
       <c r="AJ57" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK57" t="n">
         <v>32</v>
@@ -11538,13 +11538,13 @@
         <v>20</v>
       </c>
       <c r="AQ57" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT57" t="n">
         <v>12.5</v>
@@ -11553,44 +11553,44 @@
         <v>7.4</v>
       </c>
       <c r="AV57" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AX57" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AY57" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ57" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB57" t="n">
         <v>4.6</v>
       </c>
       <c r="BC57" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF57" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG57" t="n">
         <v>11</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12203,16 +12203,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G61" t="n">
         <v>1.23</v>
       </c>
       <c r="H61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="J61" t="n">
         <v>8.199999999999999</v>
@@ -12224,7 +12224,7 @@
         <v>1.01</v>
       </c>
       <c r="M61" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N61" t="n">
         <v>8.199999999999999</v>
@@ -12251,10 +12251,10 @@
         <v>1.89</v>
       </c>
       <c r="V61" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W61" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="X61" t="n">
         <v>55</v>
@@ -12275,7 +12275,7 @@
         <v>21</v>
       </c>
       <c r="AD61" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AE61" t="n">
         <v>270</v>
@@ -12311,16 +12311,16 @@
         <v>270</v>
       </c>
       <c r="AP61" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ61" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ61" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AR61" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS61" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT61" t="n">
         <v>12</v>
@@ -12332,7 +12332,7 @@
         <v>8.4</v>
       </c>
       <c r="AW61" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX61" t="n">
         <v>8.800000000000001</v>
@@ -12341,10 +12341,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ61" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA61" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BB61" t="n">
         <v>9</v>
@@ -12353,20 +12353,20 @@
         <v>11.5</v>
       </c>
       <c r="BD61" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE61" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF61" t="n">
         <v>2.68</v>
       </c>
       <c r="BG61" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
         <v>2.4</v>
       </c>
       <c r="G67" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H67" t="n">
         <v>2.82</v>
@@ -13382,7 +13382,7 @@
         <v>3.5</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -13418,7 +13418,7 @@
         <v>1.47</v>
       </c>
       <c r="W67" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X67" t="n">
         <v>21</v>
@@ -13436,13 +13436,13 @@
         <v>14.5</v>
       </c>
       <c r="AC67" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD67" t="n">
         <v>14</v>
       </c>
       <c r="AE67" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF67" t="n">
         <v>19.5</v>
@@ -13451,7 +13451,7 @@
         <v>13</v>
       </c>
       <c r="AH67" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI67" t="n">
         <v>38</v>
@@ -13472,7 +13472,7 @@
         <v>16.5</v>
       </c>
       <c r="AO67" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP67" t="n">
         <v>17.5</v>
@@ -13484,7 +13484,7 @@
         <v>18.5</v>
       </c>
       <c r="AS67" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="AT67" t="n">
         <v>11.5</v>
@@ -13496,7 +13496,7 @@
         <v>11</v>
       </c>
       <c r="AW67" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX67" t="n">
         <v>15.5</v>
@@ -13508,19 +13508,19 @@
         <v>12.5</v>
       </c>
       <c r="BA67" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB67" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC67" t="n">
         <v>20</v>
       </c>
       <c r="BD67" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE67" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF67" t="n">
         <v>13.5</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
         <v>1.2</v>
       </c>
       <c r="P68" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q68" t="n">
         <v>1.61</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -13952,13 +13952,13 @@
         <v>2.8</v>
       </c>
       <c r="G70" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H70" t="n">
         <v>2.42</v>
       </c>
       <c r="I70" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J70" t="n">
         <v>2.68</v>
@@ -13997,10 +13997,10 @@
         <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W70" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14164,31 +14164,31 @@
         <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N71" t="n">
         <v>3.5</v>
       </c>
       <c r="O71" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P71" t="n">
         <v>1.88</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R71" t="n">
         <v>1.33</v>
       </c>
       <c r="S71" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T71" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U71" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V71" t="n">
         <v>1.76</v>
@@ -14200,31 +14200,31 @@
         <v>14.5</v>
       </c>
       <c r="Y71" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z71" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA71" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB71" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC71" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD71" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF71" t="n">
         <v>25</v>
       </c>
       <c r="AG71" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH71" t="n">
         <v>19</v>
@@ -14275,10 +14275,10 @@
         <v>21</v>
       </c>
       <c r="AX71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY71" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ71" t="n">
         <v>16</v>
@@ -14287,26 +14287,26 @@
         <v>32</v>
       </c>
       <c r="BB71" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BC71" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD71" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BE71" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BF71" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG71" t="n">
         <v>16</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="G72" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="J72" t="n">
         <v>3.15</v>
       </c>
       <c r="K72" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -14364,13 +14364,13 @@
         <v>2.62</v>
       </c>
       <c r="O72" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P72" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R72" t="n">
         <v>1.24</v>
@@ -14385,10 +14385,10 @@
         <v>1.01</v>
       </c>
       <c r="V72" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W72" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14555,16 +14555,16 @@
         <v>1.06</v>
       </c>
       <c r="N73" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O73" t="n">
         <v>1.32</v>
       </c>
       <c r="P73" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -14573,7 +14573,7 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U73" t="n">
         <v>1.65</v>
@@ -14588,7 +14588,7 @@
         <v>15</v>
       </c>
       <c r="Y73" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z73" t="n">
         <v>110</v>
@@ -14603,13 +14603,13 @@
         <v>12</v>
       </c>
       <c r="AD73" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AE73" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AF73" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AG73" t="n">
         <v>11</v>
@@ -14618,7 +14618,7 @@
         <v>38</v>
       </c>
       <c r="AI73" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AJ73" t="n">
         <v>10</v>
@@ -14630,10 +14630,10 @@
         <v>55</v>
       </c>
       <c r="AM73" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN73" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO73" t="n">
         <v>400</v>
@@ -14678,10 +14678,10 @@
         <v>9.4</v>
       </c>
       <c r="BC73" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD73" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BE73" t="n">
         <v>95</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14725,25 +14725,25 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G74" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H74" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I74" t="n">
         <v>14</v>
       </c>
       <c r="J74" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K74" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M74" t="n">
         <v>1.05</v>
@@ -14755,34 +14755,34 @@
         <v>1.26</v>
       </c>
       <c r="P74" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R74" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S74" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T74" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U74" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V74" t="n">
         <v>1.07</v>
       </c>
       <c r="W74" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="X74" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y74" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z74" t="n">
         <v>1000</v>
@@ -14815,13 +14815,13 @@
         <v>1000</v>
       </c>
       <c r="AJ74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK74" t="n">
         <v>19</v>
       </c>
       <c r="AL74" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM74" t="n">
         <v>1000</v>
@@ -14833,16 +14833,16 @@
         <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ74" t="n">
         <v>22</v>
       </c>
       <c r="AR74" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS74" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AS74" t="n">
-        <v>4.6</v>
       </c>
       <c r="AT74" t="n">
         <v>6.2</v>
@@ -14851,44 +14851,44 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV74" t="n">
-        <v>28</v>
+        <v>4.1</v>
       </c>
       <c r="AW74" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX74" t="n">
         <v>6.2</v>
       </c>
       <c r="AY74" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ74" t="n">
         <v>21</v>
       </c>
       <c r="BA74" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB74" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC74" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD74" t="n">
-        <v>30</v>
+        <v>4.1</v>
       </c>
       <c r="BE74" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF74" t="n">
         <v>5</v>
       </c>
       <c r="BG74" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v>2.98</v>
       </c>
       <c r="H75" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I75" t="n">
         <v>3.1</v>
@@ -14940,7 +14940,7 @@
         <v>1.01</v>
       </c>
       <c r="M75" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N75" t="n">
         <v>2.76</v>
@@ -14973,7 +14973,7 @@
         <v>1.5</v>
       </c>
       <c r="X75" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y75" t="n">
         <v>15</v>
@@ -15030,59 +15030,59 @@
         <v>2.42</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="AR75" t="n">
         <v>11.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="AU75" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="AV75" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="AW75" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="AX75" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="AY75" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="AZ75" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="BA75" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="BB75" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="BC75" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="BD75" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="BE75" t="n">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="BF75" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="BG75" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G78" t="n">
         <v>3.55</v>
@@ -15516,7 +15516,7 @@
         <v>2.94</v>
       </c>
       <c r="K78" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L78" t="n">
         <v>1.01</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -15889,13 +15889,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G80" t="n">
         <v>3.85</v>
       </c>
       <c r="H80" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I80" t="n">
         <v>2.88</v>
@@ -15913,7 +15913,7 @@
         <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O80" t="n">
         <v>1.39</v>
@@ -15922,7 +15922,7 @@
         <v>1.7</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R80" t="n">
         <v>1.21</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
         <v>1.38</v>
       </c>
       <c r="M81" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N81" t="n">
         <v>4.2</v>
@@ -16200,7 +16200,7 @@
         <v>30</v>
       </c>
       <c r="AS81" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AT81" t="n">
         <v>9.199999999999999</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16277,19 +16277,19 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G82" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H82" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J82" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="K82" t="n">
         <v>950</v>
@@ -16301,7 +16301,7 @@
         <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O82" t="n">
         <v>1.42</v>
@@ -16310,13 +16310,13 @@
         <v>1.53</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R82" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S82" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T82" t="n">
         <v>1.01</v>
@@ -16325,10 +16325,10 @@
         <v>1.01</v>
       </c>
       <c r="V82" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W82" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X82" t="n">
         <v>1000</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16471,16 +16471,16 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G83" t="n">
         <v>1.34</v>
       </c>
       <c r="H83" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I83" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J83" t="n">
         <v>6.4</v>
@@ -16507,7 +16507,7 @@
         <v>1.44</v>
       </c>
       <c r="R83" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S83" t="n">
         <v>2.1</v>
@@ -16522,7 +16522,7 @@
         <v>1.1</v>
       </c>
       <c r="W83" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X83" t="n">
         <v>36</v>
@@ -16534,7 +16534,7 @@
         <v>110</v>
       </c>
       <c r="AA83" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB83" t="n">
         <v>13.5</v>
@@ -16543,7 +16543,7 @@
         <v>15</v>
       </c>
       <c r="AD83" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE83" t="n">
         <v>130</v>
@@ -16555,7 +16555,7 @@
         <v>10.5</v>
       </c>
       <c r="AH83" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI83" t="n">
         <v>95</v>
@@ -16594,7 +16594,7 @@
         <v>12</v>
       </c>
       <c r="AU83" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV83" t="n">
         <v>32</v>
@@ -16612,10 +16612,10 @@
         <v>22</v>
       </c>
       <c r="BA83" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BB83" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC83" t="n">
         <v>12</v>
@@ -16630,11 +16630,11 @@
         <v>3.65</v>
       </c>
       <c r="BG83" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16677,13 +16677,13 @@
         <v>14</v>
       </c>
       <c r="J84" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K84" t="n">
         <v>7.2</v>
       </c>
       <c r="L84" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M84" t="n">
         <v>1.02</v>
@@ -16710,7 +16710,7 @@
         <v>1.96</v>
       </c>
       <c r="U84" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V84" t="n">
         <v>1.08</v>
@@ -16719,16 +16719,16 @@
         <v>4.4</v>
       </c>
       <c r="X84" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y84" t="n">
         <v>1000</v>
       </c>
       <c r="Z84" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AA84" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AB84" t="n">
         <v>12</v>
@@ -16737,64 +16737,64 @@
         <v>15.5</v>
       </c>
       <c r="AD84" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE84" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF84" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG84" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH84" t="n">
         <v>29</v>
       </c>
       <c r="AI84" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ84" t="n">
         <v>10.5</v>
       </c>
       <c r="AK84" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL84" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM84" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN84" t="n">
         <v>3.75</v>
       </c>
       <c r="AO84" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP84" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="AQ84" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AR84" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AS84" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT84" t="n">
         <v>10.5</v>
       </c>
       <c r="AU84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV84" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AW84" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AX84" t="n">
         <v>8.4</v>
@@ -16803,32 +16803,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ84" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA84" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BB84" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC84" t="n">
         <v>12</v>
       </c>
       <c r="BD84" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BE84" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BF84" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG84" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
         <v>1.3</v>
       </c>
       <c r="S85" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T85" t="n">
         <v>2.1</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17056,19 +17056,19 @@
         <v>4.7</v>
       </c>
       <c r="G86" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H86" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="I86" t="n">
         <v>1.89</v>
       </c>
       <c r="J86" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K86" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L86" t="n">
         <v>1.01</v>
@@ -17077,19 +17077,19 @@
         <v>1.06</v>
       </c>
       <c r="N86" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O86" t="n">
         <v>1.32</v>
       </c>
       <c r="P86" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q86" t="n">
         <v>1.94</v>
       </c>
       <c r="R86" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S86" t="n">
         <v>3.4</v>
@@ -17098,13 +17098,13 @@
         <v>1.86</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V86" t="n">
         <v>2.12</v>
       </c>
       <c r="W86" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X86" t="n">
         <v>17</v>
@@ -17119,7 +17119,7 @@
         <v>21</v>
       </c>
       <c r="AB86" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC86" t="n">
         <v>8.800000000000001</v>
@@ -17131,31 +17131,31 @@
         <v>20</v>
       </c>
       <c r="AF86" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG86" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH86" t="n">
         <v>20</v>
       </c>
-      <c r="AH86" t="n">
-        <v>21</v>
-      </c>
       <c r="AI86" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ86" t="n">
         <v>140</v>
       </c>
       <c r="AK86" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL86" t="n">
         <v>75</v>
       </c>
       <c r="AM86" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN86" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO86" t="n">
         <v>13</v>
@@ -17164,13 +17164,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ86" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR86" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS86" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT86" t="n">
         <v>14.5</v>
@@ -17185,38 +17185,38 @@
         <v>17</v>
       </c>
       <c r="AX86" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY86" t="n">
         <v>17</v>
       </c>
       <c r="AZ86" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA86" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB86" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD86" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE86" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF86" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG86" t="n">
         <v>11</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17247,13 +17247,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G87" t="n">
         <v>3.7</v>
       </c>
       <c r="H87" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I87" t="n">
         <v>2.86</v>
@@ -17262,7 +17262,7 @@
         <v>3.05</v>
       </c>
       <c r="K87" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G88" t="n">
         <v>2.72</v>
@@ -17465,13 +17465,13 @@
         <v>1.11</v>
       </c>
       <c r="N88" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O88" t="n">
         <v>1.51</v>
       </c>
       <c r="P88" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q88" t="n">
         <v>2.62</v>
@@ -17516,7 +17516,7 @@
         <v>19</v>
       </c>
       <c r="AE88" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF88" t="n">
         <v>18</v>
@@ -17525,7 +17525,7 @@
         <v>15.5</v>
       </c>
       <c r="AH88" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI88" t="n">
         <v>1000</v>
@@ -17582,29 +17582,29 @@
         <v>17.5</v>
       </c>
       <c r="BA88" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB88" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC88" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD88" t="n">
         <v>4.2</v>
       </c>
       <c r="BE88" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF88" t="n">
         <v>4.1</v>
       </c>
       <c r="BG88" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17635,10 +17635,10 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="G89" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
         <v>4.6</v>
@@ -17647,7 +17647,7 @@
         <v>8</v>
       </c>
       <c r="J89" t="n">
-        <v>1.09</v>
+        <v>2.64</v>
       </c>
       <c r="K89" t="n">
         <v>950</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
         <v>3.45</v>
       </c>
       <c r="G90" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H90" t="n">
         <v>1.74</v>
@@ -17880,7 +17880,7 @@
         <v>1.74</v>
       </c>
       <c r="W90" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X90" t="n">
         <v>1000</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18241,16 +18241,16 @@
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O92" t="n">
         <v>1.28</v>
       </c>
       <c r="P92" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R92" t="n">
         <v>1.3</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18605,13 +18605,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="G94" t="n">
         <v>1.68</v>
       </c>
       <c r="H94" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I94" t="n">
         <v>12</v>
@@ -18620,7 +18620,7 @@
         <v>4</v>
       </c>
       <c r="K94" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L94" t="n">
         <v>1.01</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18802,13 +18802,13 @@
         <v>2.22</v>
       </c>
       <c r="G95" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H95" t="n">
         <v>2.66</v>
       </c>
       <c r="I95" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J95" t="n">
         <v>1.09</v>
@@ -18847,16 +18847,16 @@
         <v>1.01</v>
       </c>
       <c r="V95" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W95" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X95" t="n">
         <v>24</v>
       </c>
       <c r="Y95" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z95" t="n">
         <v>30</v>
@@ -18904,65 +18904,65 @@
         <v>23</v>
       </c>
       <c r="AO95" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP95" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AQ95" t="n">
         <v>10</v>
       </c>
       <c r="AR95" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AS95" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AU95" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AV95" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AX95" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AY95" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AZ95" t="n">
         <v>11.5</v>
       </c>
       <c r="BA95" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB95" t="n">
         <v>3.2</v>
-      </c>
-      <c r="BB95" t="n">
-        <v>3.15</v>
       </c>
       <c r="BC95" t="n">
         <v>18</v>
       </c>
       <c r="BD95" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BE95" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BF95" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG95" t="n">
         <v>17</v>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>
@@ -18996,7 +18996,7 @@
         <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H96" t="n">
         <v>4.2</v>
@@ -19005,158 +19005,158 @@
         <v>5</v>
       </c>
       <c r="J96" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K96" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L96" t="n">
         <v>1.01</v>
       </c>
       <c r="M96" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N96" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="O96" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P96" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R96" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S96" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="U96" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="V96" t="n">
         <v>1.25</v>
       </c>
       <c r="W96" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X96" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y96" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z96" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA96" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB96" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC96" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ96" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD96" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK96" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL96" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN96" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP96" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR96" t="n">
-        <v>2.36</v>
+        <v>6.8</v>
       </c>
       <c r="AS96" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="AT96" t="n">
-        <v>1.99</v>
+        <v>5.9</v>
       </c>
       <c r="AU96" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV96" t="n">
-        <v>2.26</v>
+        <v>16.5</v>
       </c>
       <c r="AW96" t="n">
-        <v>2.48</v>
+        <v>7.8</v>
       </c>
       <c r="AX96" t="n">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="AY96" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="AZ96" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA96" t="n">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB96" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="BC96" t="n">
-        <v>2.34</v>
+        <v>6.6</v>
       </c>
       <c r="BD96" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE96" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="BF96" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BG96" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-09 00:39:43</t>
+          <t>2026-04-09 02:58:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,93 +743,93 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="G2" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="K2" t="n">
-        <v>1.19</v>
+        <v>1.87</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1</v>
+        <v>34</v>
       </c>
       <c r="T2" t="n">
         <v>1.42</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.22</v>
+        <v>2.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>820</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -838,7 +838,7 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.17</v>
+        <v>2.32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>55</v>
+        <v>2.52</v>
       </c>
       <c r="AS2" t="n">
-        <v>46</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>46</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>46</v>
+        <v>2.64</v>
       </c>
       <c r="AW2" t="n">
-        <v>46</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>46</v>
+        <v>2.64</v>
       </c>
       <c r="AY2" t="n">
-        <v>46</v>
+        <v>2.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>46</v>
+        <v>2.64</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>46</v>
+        <v>2.64</v>
       </c>
       <c r="BC2" t="n">
-        <v>46</v>
+        <v>2.64</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>2.64</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.5</v>
+        <v>2.64</v>
       </c>
       <c r="BF2" t="n">
-        <v>27</v>
+        <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>27</v>
+        <v>2.64</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club 2 de Mayo de Pedro </t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>690</v>
+        <v>1.33</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>690</v>
+        <v>5.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -975,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.1</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
+        <v>160</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,25 +1017,25 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="AH3" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.6</v>
+        <v>1.37</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.17</v>
+        <v>42</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.17</v>
+        <v>210</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.17</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.17</v>
+        <v>34</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.17</v>
+        <v>170</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.17</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>170</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.17</v>
+        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.17</v>
+        <v>9.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.17</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.17</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.94</v>
+        <v>1.14</v>
       </c>
       <c r="G4" t="n">
-        <v>1.97</v>
+        <v>1.15</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>55</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.4</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.72</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="S4" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>2.02</v>
+        <v>7.4</v>
       </c>
       <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AK4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>340</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP4" t="n">
+      <c r="AZ4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>120</v>
+      </c>
+      <c r="BB4" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
+      <c r="BC4" t="n">
         <v>24</v>
       </c>
-      <c r="BA4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>22</v>
-      </c>
       <c r="BD4" t="n">
+        <v>140</v>
+      </c>
+      <c r="BE4" t="n">
         <v>50</v>
       </c>
-      <c r="BE4" t="n">
-        <v>26</v>
-      </c>
       <c r="BF4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BG4" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>4.3</v>
       </c>
-      <c r="G5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>2.48</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>2.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>6.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>570</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>420</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX5" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21</v>
-      </c>
       <c r="AY5" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>350</v>
       </c>
       <c r="BF5" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BG5" t="n">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>4.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.59</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I6" t="n">
+      <c r="AH6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>530</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>55</v>
-      </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="AW6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX6" t="n">
         <v>20</v>
       </c>
-      <c r="AX6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB6" t="n">
         <v>20</v>
       </c>
-      <c r="BB6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD6" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BE6" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>2.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.76</v>
+        <v>2.54</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AM7" t="n">
-        <v>230</v>
+        <v>420</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="AP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV7" t="n">
         <v>11</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW7" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BD7" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>190</v>
       </c>
       <c r="BF7" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.199999999999999</v>
+        <v>100</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OHiggins</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="G8" t="n">
-        <v>2.24</v>
+        <v>1.18</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>38</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>44</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.81</v>
+        <v>6.4</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>550</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
         <v>14</v>
       </c>
-      <c r="Z8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AO8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>240</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>85</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF8" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB8" t="n">
+      <c r="BG8" t="n">
         <v>24</v>
       </c>
-      <c r="BC8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>38</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,114 +2101,114 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>690</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>690</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.45</v>
       </c>
-      <c r="G9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>1.07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.06</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>990</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.6</v>
+        <v>990</v>
       </c>
       <c r="AE9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>990</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>990</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2220,72 +2220,72 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>1.29</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.5</v>
+        <v>1.29</v>
       </c>
       <c r="AS9" t="n">
-        <v>24</v>
+        <v>1.29</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>1.19</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>1.15</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>1.29</v>
       </c>
       <c r="AX9" t="n">
-        <v>18</v>
+        <v>1.29</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.5</v>
+        <v>1.29</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>1.29</v>
       </c>
       <c r="BA9" t="n">
-        <v>40</v>
+        <v>1.29</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>1.29</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>1.29</v>
       </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>1.29</v>
       </c>
       <c r="BE9" t="n">
-        <v>13</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>1.29</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>1.29</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,84 +2295,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:05:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="G10" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="H10" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="I10" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.14</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AA10" t="n">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="AB10" t="n">
         <v>7.2</v>
@@ -2381,486 +2381,98 @@
         <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
-        <v>150</v>
+        <v>970</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
         <v>27</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>960</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>920</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF10" t="n">
         <v>13</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BG10" t="n">
         <v>15</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mexican Liga MX</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Puebla</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Leon</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-04-10 19:45:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>22:05:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Deportivo Pasto</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
